--- a/CSVDatas/InteractivesCSV.xlsx
+++ b/CSVDatas/InteractivesCSV.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Personal Files\Unreal5\PotenUp\_TeamProjects\3T_ReTri\ReTri\CSVDatas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PU_Project\_TeamProjects\Retri\_Git\ReTri\CSVDatas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96CE9A08-440D-46C2-AD97-7DFF468F8ABB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCAA6580-AC10-4F1A-812F-5AFB601CC424}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6660" yWindow="2880" windowWidth="21600" windowHeight="10830" activeTab="1" xr2:uid="{AFBEF995-9824-4DBC-9BD6-E0A7B4B73573}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="2" xr2:uid="{AFBEF995-9824-4DBC-9BD6-E0A7B4B73573}"/>
   </bookViews>
   <sheets>
     <sheet name="ChaosData" sheetId="1" r:id="rId1"/>
     <sheet name="CurseData" sheetId="2" r:id="rId2"/>
+    <sheet name="CurseRewardData" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="59">
   <si>
     <t>ChaosName</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -193,6 +194,69 @@
   </si>
   <si>
     <t>Name</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CurseMonster</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CurseMap</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RewardGold</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RewardDreamPowder</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RewardAttackDamage</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RewardAttackSpeed</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RewardType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RewardMaxHP</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RewardMemoryHaste</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Info</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>증오는 손을 뻗더니 끔찍한 냄새가 나는 금 조각을 당신에게 건넵니다.</t>
+  </si>
+  <si>
+    <t>증오는 손을 뻗더니 불쾌한 냄새가 나는 꿈의 가루를 당신에게 건넵니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>증오는 손을 뻗더니 오묘한 냄새가 나는 포션을 당신에게 건넵니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>증오는 손을 뻗더니 기괴한 냄새가 나는 환단을 당신에게 건넵니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>증오는 손을 뻗더니 기묘한 냄새가 나는 이클립스를 당신에게 건넵니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RewardLevel</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -239,8 +303,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -715,10 +782,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC035209-C671-4912-9D91-EBFB7F683844}">
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="11.375" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>42</v>
       </c>
@@ -734,8 +804,14 @@
       <c r="E1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -751,8 +827,14 @@
       <c r="E2" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F2">
+        <v>5</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -768,8 +850,14 @@
       <c r="E3" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F3">
+        <v>7</v>
+      </c>
+      <c r="G3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>22</v>
       </c>
@@ -785,6 +873,101 @@
       <c r="E4" t="s">
         <v>29</v>
       </c>
+      <c r="F4">
+        <v>10</v>
+      </c>
+      <c r="G4">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1DF09098-0D79-49D4-B623-910E4D683D59}">
+  <dimension ref="A1:D8"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="3" width="12.25" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C2" s="1"/>
+      <c r="D2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C3" s="1"/>
+      <c r="D3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C4" s="1"/>
+      <c r="D4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C5" s="1"/>
+      <c r="D5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B6" t="s">
+        <v>51</v>
+      </c>
+      <c r="C6" s="1"/>
+      <c r="D6" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D8" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/CSVDatas/InteractivesCSV.xlsx
+++ b/CSVDatas/InteractivesCSV.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PU_Project\_TeamProjects\Retri\_Git\ReTri\CSVDatas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCAA6580-AC10-4F1A-812F-5AFB601CC424}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57D95785-066C-4DC5-BB3F-DEF106E64C91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="2" xr2:uid="{AFBEF995-9824-4DBC-9BD6-E0A7B4B73573}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="3" xr2:uid="{AFBEF995-9824-4DBC-9BD6-E0A7B4B73573}"/>
   </bookViews>
   <sheets>
     <sheet name="ChaosData" sheetId="1" r:id="rId1"/>
     <sheet name="CurseData" sheetId="2" r:id="rId2"/>
     <sheet name="CurseRewardData" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="86">
   <si>
     <t>ChaosName</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -257,6 +258,95 @@
   </si>
   <si>
     <t>RewardLevel</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">RewardMaxHP          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RewardAttackPower      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RewardSpellPower       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RewardProjectileSpeed   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RewardAttackSpeed      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RewardMoveSpeed       </t>
+  </si>
+  <si>
+    <t>RewardMemoryAcceleration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MaxHP            </t>
+  </si>
+  <si>
+    <t xml:space="preserve">AttackPower    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SpellPower     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ProjectileSpeed </t>
+  </si>
+  <si>
+    <t xml:space="preserve">AttackSpeed    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MoveSpeed         </t>
+  </si>
+  <si>
+    <t>MemoryAcceleration</t>
+  </si>
+  <si>
+    <t>WellRewardName</t>
+  </si>
+  <si>
+    <t>WellRewardType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RewardAmount</t>
+  </si>
+  <si>
+    <t>DreamDustCost</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>WellRewardNameKR</t>
+  </si>
+  <si>
+    <t>최대 체력</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>공격력</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>기억 피해량</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>총알 속도</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>공격 속도</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이동 속도</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>기억 가속</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -974,4 +1064,182 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D27CFD3C-CA6B-4813-BFDF-38411E5B43A8}">
+  <dimension ref="A1:G8"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="24.625" customWidth="1"/>
+    <col min="2" max="2" width="18.25" customWidth="1"/>
+    <col min="3" max="3" width="24.5" customWidth="1"/>
+    <col min="4" max="4" width="18" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1" t="s">
+        <v>76</v>
+      </c>
+      <c r="F1" t="s">
+        <v>75</v>
+      </c>
+      <c r="G1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E2">
+        <v>100</v>
+      </c>
+      <c r="F2">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C3" t="s">
+        <v>80</v>
+      </c>
+      <c r="D3" t="s">
+        <v>60</v>
+      </c>
+      <c r="E3">
+        <v>150</v>
+      </c>
+      <c r="F3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D4" t="s">
+        <v>61</v>
+      </c>
+      <c r="E4">
+        <v>150</v>
+      </c>
+      <c r="F4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B5" t="s">
+        <v>69</v>
+      </c>
+      <c r="C5" t="s">
+        <v>82</v>
+      </c>
+      <c r="D5" t="s">
+        <v>62</v>
+      </c>
+      <c r="E5">
+        <v>200</v>
+      </c>
+      <c r="F5">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>63</v>
+      </c>
+      <c r="B6" t="s">
+        <v>70</v>
+      </c>
+      <c r="C6" t="s">
+        <v>83</v>
+      </c>
+      <c r="D6" t="s">
+        <v>63</v>
+      </c>
+      <c r="E6">
+        <v>300</v>
+      </c>
+      <c r="F6">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>64</v>
+      </c>
+      <c r="B7" t="s">
+        <v>71</v>
+      </c>
+      <c r="C7" t="s">
+        <v>84</v>
+      </c>
+      <c r="D7" t="s">
+        <v>64</v>
+      </c>
+      <c r="E7">
+        <v>300</v>
+      </c>
+      <c r="F7">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>65</v>
+      </c>
+      <c r="B8" t="s">
+        <v>72</v>
+      </c>
+      <c r="C8" t="s">
+        <v>85</v>
+      </c>
+      <c r="D8" t="s">
+        <v>65</v>
+      </c>
+      <c r="E8">
+        <v>250</v>
+      </c>
+      <c r="F8">
+        <v>120</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/CSVDatas/InteractivesCSV.xlsx
+++ b/CSVDatas/InteractivesCSV.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PU_Project\_TeamProjects\Retri\_Git\ReTri\CSVDatas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57D95785-066C-4DC5-BB3F-DEF106E64C91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E64625BA-F49E-493F-8238-04CA99C4ED7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="3" xr2:uid="{AFBEF995-9824-4DBC-9BD6-E0A7B4B73573}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="4" xr2:uid="{AFBEF995-9824-4DBC-9BD6-E0A7B4B73573}"/>
   </bookViews>
   <sheets>
     <sheet name="ChaosData" sheetId="1" r:id="rId1"/>
     <sheet name="CurseData" sheetId="2" r:id="rId2"/>
     <sheet name="CurseRewardData" sheetId="3" r:id="rId3"/>
-    <sheet name="Sheet1" sheetId="4" r:id="rId4"/>
+    <sheet name="WellData" sheetId="4" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="90">
   <si>
     <t>ChaosName</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -348,6 +349,19 @@
   <si>
     <t>기억 가속</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dialog</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>내 물건보다 네 목숨값이 싸다는 걸 명심해라.</t>
+  </si>
+  <si>
+    <t>이 던전에서 나대던 놈들이 다 어디로 갔을 것 같나.</t>
+  </si>
+  <si>
+    <t>진열장에 네 머리통이 올라가고 싶지 않으면 얌전히 굴어라.</t>
   </si>
 </sst>
 </file>
@@ -1242,4 +1256,44 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21E1BD7E-8283-4E2C-8885-CB8E7B30C4AD}">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>89</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/CSVDatas/InteractivesCSV.xlsx
+++ b/CSVDatas/InteractivesCSV.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PU_Project\_TeamProjects\Retri\_Git\ReTri\CSVDatas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E64625BA-F49E-493F-8238-04CA99C4ED7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5496B5B5-533C-4B83-A296-331B32C4DB86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="4" xr2:uid="{AFBEF995-9824-4DBC-9BD6-E0A7B4B73573}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="CurseData" sheetId="2" r:id="rId2"/>
     <sheet name="CurseRewardData" sheetId="3" r:id="rId3"/>
     <sheet name="WellData" sheetId="4" r:id="rId4"/>
-    <sheet name="Sheet1" sheetId="5" r:id="rId5"/>
+    <sheet name="MerchantDialog" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="92">
   <si>
     <t>ChaosName</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -362,6 +362,12 @@
   </si>
   <si>
     <t>진열장에 네 머리통이 올라가고 싶지 않으면 얌전히 굴어라.</t>
+  </si>
+  <si>
+    <t>실수라고 쳐두지. 다음은 없다.</t>
+  </si>
+  <si>
+    <t>여기가 왜 여태 안 털렸는지, 생각 안 해봤나?</t>
   </si>
 </sst>
 </file>
@@ -1260,7 +1266,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21E1BD7E-8283-4E2C-8885-CB8E7B30C4AD}">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
@@ -1292,6 +1298,22 @@
         <v>89</v>
       </c>
     </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>91</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
